--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/24.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/24.xlsx
@@ -426,13 +426,13 @@
         <v>-13.29011110018972</v>
       </c>
       <c r="E2">
-        <v>-8.022438318892055</v>
+        <v>-16.33839666083168</v>
       </c>
       <c r="F2">
-        <v>-1.414760550814755</v>
+        <v>-1.469920707799772</v>
       </c>
       <c r="G2">
-        <v>-12.1287640792577</v>
+        <v>-13.58951746936957</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.76842862177808</v>
       </c>
       <c r="E3">
-        <v>-7.856582958361128</v>
+        <v>-17.23869804982261</v>
       </c>
       <c r="F3">
-        <v>-1.319679711954025</v>
+        <v>-1.351366421845912</v>
       </c>
       <c r="G3">
-        <v>-12.05789523089852</v>
+        <v>-13.7895257333974</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.09872094109415</v>
       </c>
       <c r="E4">
-        <v>-9.118070905729844</v>
+        <v>-17.71326854040444</v>
       </c>
       <c r="F4">
-        <v>-1.32187654230625</v>
+        <v>-1.639944773959176</v>
       </c>
       <c r="G4">
-        <v>-12.01242488791663</v>
+        <v>-13.51685265005533</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.20738049096588</v>
       </c>
       <c r="E5">
-        <v>-10.84951030019257</v>
+        <v>-17.50444249001473</v>
       </c>
       <c r="F5">
-        <v>-0.474813715592962</v>
+        <v>-1.037442512309192</v>
       </c>
       <c r="G5">
-        <v>-13.16312748027529</v>
+        <v>-12.96897391603365</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.09766194495394</v>
       </c>
       <c r="E6">
-        <v>-10.75273228217464</v>
+        <v>-18.96784603643745</v>
       </c>
       <c r="F6">
-        <v>-0.7821396787663841</v>
+        <v>-1.344250745855864</v>
       </c>
       <c r="G6">
-        <v>-12.1865430305546</v>
+        <v>-13.74535146899414</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.77245400162416</v>
       </c>
       <c r="E7">
-        <v>-11.45985349847237</v>
+        <v>-18.83277977068468</v>
       </c>
       <c r="F7">
-        <v>-0.3821583364876289</v>
+        <v>-1.074545088280582</v>
       </c>
       <c r="G7">
-        <v>-11.7624820102472</v>
+        <v>-12.66192081726625</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.24924390763595</v>
       </c>
       <c r="E8">
-        <v>-12.48170818677719</v>
+        <v>-18.26068406387366</v>
       </c>
       <c r="F8">
-        <v>-0.1923727375670397</v>
+        <v>-1.0880731563357</v>
       </c>
       <c r="G8">
-        <v>-11.5652297753808</v>
+        <v>-13.05023125629506</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.53516565363236</v>
       </c>
       <c r="E9">
-        <v>-12.81623561867182</v>
+        <v>-20.08781917106647</v>
       </c>
       <c r="F9">
-        <v>0.1313664973254519</v>
+        <v>-0.8155203999969959</v>
       </c>
       <c r="G9">
-        <v>-11.2358205625867</v>
+        <v>-12.68283353343782</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.65423195033337</v>
       </c>
       <c r="E10">
-        <v>-14.02411096226372</v>
+        <v>-19.56399699717722</v>
       </c>
       <c r="F10">
-        <v>0.4466149663392485</v>
+        <v>-0.7545442754769243</v>
       </c>
       <c r="G10">
-        <v>-10.12450021996322</v>
+        <v>-12.1660838591219</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.63655812582101</v>
       </c>
       <c r="E11">
-        <v>-14.12793528583758</v>
+        <v>-20.92535138183709</v>
       </c>
       <c r="F11">
-        <v>0.4579221813874618</v>
+        <v>-0.7426779124318214</v>
       </c>
       <c r="G11">
-        <v>-9.899664519663613</v>
+        <v>-12.03486376558181</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.507181859325344</v>
       </c>
       <c r="E12">
-        <v>-16.31512030443225</v>
+        <v>-21.58860979889652</v>
       </c>
       <c r="F12">
-        <v>0.7360399099381734</v>
+        <v>-0.676424259188514</v>
       </c>
       <c r="G12">
-        <v>-9.363409111030309</v>
+        <v>-11.72725780570935</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.285899569745037</v>
       </c>
       <c r="E13">
-        <v>-16.37710605664924</v>
+        <v>-23.10465685565841</v>
       </c>
       <c r="F13">
-        <v>0.3470998767713327</v>
+        <v>-0.4765557722410493</v>
       </c>
       <c r="G13">
-        <v>-9.230126547619252</v>
+        <v>-10.65341283859042</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.011362782684379</v>
       </c>
       <c r="E14">
-        <v>-16.71067345205424</v>
+        <v>-23.28140772465179</v>
       </c>
       <c r="F14">
-        <v>0.9140047060208135</v>
+        <v>-0.4912833162954218</v>
       </c>
       <c r="G14">
-        <v>-7.60800558101392</v>
+        <v>-11.04789082395889</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.709272977998652</v>
       </c>
       <c r="E15">
-        <v>-18.54951466455688</v>
+        <v>-23.77785527316468</v>
       </c>
       <c r="F15">
-        <v>0.7884043269387413</v>
+        <v>-0.1511001600899572</v>
       </c>
       <c r="G15">
-        <v>-8.633152423250175</v>
+        <v>-9.350991254712504</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.402072227908411</v>
       </c>
       <c r="E16">
-        <v>-18.35867571292564</v>
+        <v>-25.06364754053256</v>
       </c>
       <c r="F16">
-        <v>1.182957377626952</v>
+        <v>-0.1153867562530621</v>
       </c>
       <c r="G16">
-        <v>-7.713655020808681</v>
+        <v>-9.587357585125387</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.125249921403907</v>
       </c>
       <c r="E17">
-        <v>-18.95333680571688</v>
+        <v>-26.0689823556574</v>
       </c>
       <c r="F17">
-        <v>1.564485179273542</v>
+        <v>0.1146268488496794</v>
       </c>
       <c r="G17">
-        <v>-6.319577673130506</v>
+        <v>-9.618013236819039</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.905395455816262</v>
       </c>
       <c r="E18">
-        <v>-19.81899084007513</v>
+        <v>-26.56587369462304</v>
       </c>
       <c r="F18">
-        <v>1.227480468792619</v>
+        <v>0.3589471873661712</v>
       </c>
       <c r="G18">
-        <v>-5.795756673542705</v>
+        <v>-8.962005464393679</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7609867313690434</v>
       </c>
       <c r="E19">
-        <v>-20.58572941668384</v>
+        <v>-27.72598269438204</v>
       </c>
       <c r="F19">
-        <v>1.732092069351577</v>
+        <v>0.4259306322913449</v>
       </c>
       <c r="G19">
-        <v>-5.814385113292183</v>
+        <v>-7.751041011583671</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2860392675721086</v>
       </c>
       <c r="E20">
-        <v>-22.201710837847</v>
+        <v>-27.6983273036172</v>
       </c>
       <c r="F20">
-        <v>1.854778251910601</v>
+        <v>0.9196641121167398</v>
       </c>
       <c r="G20">
-        <v>-5.688375818430904</v>
+        <v>-8.111787848452513</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.214410383891581</v>
       </c>
       <c r="E21">
-        <v>-22.7226121460013</v>
+        <v>-28.19841121675824</v>
       </c>
       <c r="F21">
-        <v>2.195136193638056</v>
+        <v>1.118813576158574</v>
       </c>
       <c r="G21">
-        <v>-4.673177165540159</v>
+        <v>-8.161290435901234</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.013483147981234</v>
       </c>
       <c r="E22">
-        <v>-23.06522743247362</v>
+        <v>-28.79782267878353</v>
       </c>
       <c r="F22">
-        <v>2.175757366616965</v>
+        <v>0.7226104176039878</v>
       </c>
       <c r="G22">
-        <v>-4.030438059636198</v>
+        <v>-7.127135599252624</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.677545689153561</v>
       </c>
       <c r="E23">
-        <v>-23.65677746362159</v>
+        <v>-28.90559130321807</v>
       </c>
       <c r="F23">
-        <v>2.344426223705389</v>
+        <v>1.001742067855726</v>
       </c>
       <c r="G23">
-        <v>-4.376519179766068</v>
+        <v>-7.412653599287067</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.194519046821827</v>
       </c>
       <c r="E24">
-        <v>-24.39968268152793</v>
+        <v>-30.0472377144478</v>
       </c>
       <c r="F24">
-        <v>2.554289791735032</v>
+        <v>1.012494276744064</v>
       </c>
       <c r="G24">
-        <v>-3.487283474099053</v>
+        <v>-6.859838841866329</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.564172776285018</v>
       </c>
       <c r="E25">
-        <v>-24.86846578232796</v>
+        <v>-30.43513321252282</v>
       </c>
       <c r="F25">
-        <v>2.373089392577057</v>
+        <v>1.117788057313909</v>
       </c>
       <c r="G25">
-        <v>-3.800576951207981</v>
+        <v>-7.372976710998901</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.79025848331336</v>
       </c>
       <c r="E26">
-        <v>-25.17381625619117</v>
+        <v>-29.42427818758262</v>
       </c>
       <c r="F26">
-        <v>2.341251919817861</v>
+        <v>1.417391979558434</v>
       </c>
       <c r="G26">
-        <v>-4.065943660544881</v>
+        <v>-6.224492184151559</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.875252918240216</v>
       </c>
       <c r="E27">
-        <v>-25.27009161359424</v>
+        <v>-30.34974883510819</v>
       </c>
       <c r="F27">
-        <v>2.380074186517462</v>
+        <v>1.317873576520907</v>
       </c>
       <c r="G27">
-        <v>-3.680453806315526</v>
+        <v>-6.804870543732269</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.825558406383408</v>
       </c>
       <c r="E28">
-        <v>-25.65292427772868</v>
+        <v>-30.11158053738578</v>
       </c>
       <c r="F28">
-        <v>2.747365665979541</v>
+        <v>1.015835910846957</v>
       </c>
       <c r="G28">
-        <v>-3.981524749293466</v>
+        <v>-7.24198173455548</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.651147279689966</v>
       </c>
       <c r="E29">
-        <v>-25.48174796023874</v>
+        <v>-30.01192920260999</v>
       </c>
       <c r="F29">
-        <v>2.598312548989409</v>
+        <v>1.053717152176978</v>
       </c>
       <c r="G29">
-        <v>-3.906163490637497</v>
+        <v>-7.749432086451585</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.364769935003096</v>
       </c>
       <c r="E30">
-        <v>-24.65430066108321</v>
+        <v>-30.75950101298123</v>
       </c>
       <c r="F30">
-        <v>2.611526665798867</v>
+        <v>1.354880061873572</v>
       </c>
       <c r="G30">
-        <v>-4.612782883267236</v>
+        <v>-7.30239588010164</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.977905652029639</v>
       </c>
       <c r="E31">
-        <v>-24.84807859234543</v>
+        <v>-30.484244513136</v>
       </c>
       <c r="F31">
-        <v>2.446048679946026</v>
+        <v>1.613786293618557</v>
       </c>
       <c r="G31">
-        <v>-3.383368760166869</v>
+        <v>-7.068836892306058</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.503962289727887</v>
       </c>
       <c r="E32">
-        <v>-24.41557762529485</v>
+        <v>-30.27948050393117</v>
       </c>
       <c r="F32">
-        <v>2.622739446963161</v>
+        <v>1.184978594089782</v>
       </c>
       <c r="G32">
-        <v>-4.453406599915642</v>
+        <v>-7.222091976955539</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.957596548129708</v>
       </c>
       <c r="E33">
-        <v>-24.07775799279666</v>
+        <v>-28.85621735111244</v>
       </c>
       <c r="F33">
-        <v>2.598211488166267</v>
+        <v>1.270245764329547</v>
       </c>
       <c r="G33">
-        <v>-4.19100282883639</v>
+        <v>-7.400901162622654</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.354999117918313</v>
       </c>
       <c r="E34">
-        <v>-24.50040047193253</v>
+        <v>-29.04974168783023</v>
       </c>
       <c r="F34">
-        <v>2.655610722241051</v>
+        <v>1.442474944515203</v>
       </c>
       <c r="G34">
-        <v>-4.786242227342888</v>
+        <v>-8.413712912179584</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.7080559580185496</v>
       </c>
       <c r="E35">
-        <v>-24.93181460522126</v>
+        <v>-28.8566656700392</v>
       </c>
       <c r="F35">
-        <v>2.26014315394015</v>
+        <v>1.450624423023944</v>
       </c>
       <c r="G35">
-        <v>-4.677341831828563</v>
+        <v>-7.705580600238399</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.02805254709584252</v>
       </c>
       <c r="E36">
-        <v>-22.87446546490051</v>
+        <v>-28.45685575685</v>
       </c>
       <c r="F36">
-        <v>2.490252021294213</v>
+        <v>1.056929560965035</v>
       </c>
       <c r="G36">
-        <v>-4.855604777481698</v>
+        <v>-8.411683547764012</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6690043558735665</v>
       </c>
       <c r="E37">
-        <v>-23.07948306864977</v>
+        <v>-28.23149624785828</v>
       </c>
       <c r="F37">
-        <v>2.87793624947841</v>
+        <v>1.652297094174707</v>
       </c>
       <c r="G37">
-        <v>-5.374450027123975</v>
+        <v>-8.406101967984799</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.37402757435203</v>
       </c>
       <c r="E38">
-        <v>-22.03185683476729</v>
+        <v>-27.85855377095659</v>
       </c>
       <c r="F38">
-        <v>2.818694726299801</v>
+        <v>1.1761067792058</v>
       </c>
       <c r="G38">
-        <v>-6.071743612969587</v>
+        <v>-8.341433771420677</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.078936443625992</v>
       </c>
       <c r="E39">
-        <v>-21.36157928299598</v>
+        <v>-27.67605173997347</v>
       </c>
       <c r="F39">
-        <v>2.770467176108814</v>
+        <v>1.727971769890053</v>
       </c>
       <c r="G39">
-        <v>-6.635721529948747</v>
+        <v>-8.073832443844768</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.770788749496186</v>
       </c>
       <c r="E40">
-        <v>-21.23468238435304</v>
+        <v>-26.71292683107412</v>
       </c>
       <c r="F40">
-        <v>2.707801182087031</v>
+        <v>1.105531533222087</v>
       </c>
       <c r="G40">
-        <v>-6.197176872907033</v>
+        <v>-7.87577905695787</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.441702243717279</v>
       </c>
       <c r="E41">
-        <v>-20.67238629529461</v>
+        <v>-26.25824086985997</v>
       </c>
       <c r="F41">
-        <v>3.202896497922628</v>
+        <v>1.192631052156844</v>
       </c>
       <c r="G41">
-        <v>-6.166395420482889</v>
+        <v>-7.853710960393088</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.089492948575376</v>
       </c>
       <c r="E42">
-        <v>-18.41267776546711</v>
+        <v>-26.28939224255873</v>
       </c>
       <c r="F42">
-        <v>2.9158970140791</v>
+        <v>1.46898932834401</v>
       </c>
       <c r="G42">
-        <v>-6.14504240175459</v>
+        <v>-7.299585226938799</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.710449322399104</v>
       </c>
       <c r="E43">
-        <v>-18.82193860391031</v>
+        <v>-23.49560001674059</v>
       </c>
       <c r="F43">
-        <v>3.052991819242418</v>
+        <v>1.832582975719991</v>
       </c>
       <c r="G43">
-        <v>-6.997431735569517</v>
+        <v>-8.438684357182307</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.300420381159848</v>
       </c>
       <c r="E44">
-        <v>-16.6719821701327</v>
+        <v>-23.76310150484769</v>
       </c>
       <c r="F44">
-        <v>2.300206315009146</v>
+        <v>1.328842817668778</v>
       </c>
       <c r="G44">
-        <v>-7.271217162212784</v>
+        <v>-8.44057798923077</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.864044907523452</v>
       </c>
       <c r="E45">
-        <v>-17.20108001624089</v>
+        <v>-23.67150406109454</v>
       </c>
       <c r="F45">
-        <v>3.063349725247023</v>
+        <v>1.501249268478633</v>
       </c>
       <c r="G45">
-        <v>-6.629636747247567</v>
+        <v>-8.113016060847583</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.402872557883021</v>
       </c>
       <c r="E46">
-        <v>-17.0930442118399</v>
+        <v>-22.55142677156335</v>
       </c>
       <c r="F46">
-        <v>2.78786786177202</v>
+        <v>1.383602873198242</v>
       </c>
       <c r="G46">
-        <v>-7.580468463218263</v>
+        <v>-8.455144389603564</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.909635263393989</v>
       </c>
       <c r="E47">
-        <v>-16.67665102683461</v>
+        <v>-22.44116295795058</v>
       </c>
       <c r="F47">
-        <v>2.839326044833925</v>
+        <v>1.33638593123867</v>
       </c>
       <c r="G47">
-        <v>-7.184239199259512</v>
+        <v>-8.835439997881801</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.38899365108219</v>
       </c>
       <c r="E48">
-        <v>-15.68631904609718</v>
+        <v>-21.94890424789479</v>
       </c>
       <c r="F48">
-        <v>2.67184340986631</v>
+        <v>1.432569327112526</v>
       </c>
       <c r="G48">
-        <v>-7.669793602958878</v>
+        <v>-9.527592306504925</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.84125221371931</v>
       </c>
       <c r="E49">
-        <v>-14.66866225319747</v>
+        <v>-22.04966279456545</v>
       </c>
       <c r="F49">
-        <v>2.847212102508577</v>
+        <v>1.516249345408527</v>
       </c>
       <c r="G49">
-        <v>-8.025071418596843</v>
+        <v>-8.842378901332115</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.257460584193177</v>
       </c>
       <c r="E50">
-        <v>-14.02617141793722</v>
+        <v>-21.20789646059767</v>
       </c>
       <c r="F50">
-        <v>2.618945524258339</v>
+        <v>1.363145511818705</v>
       </c>
       <c r="G50">
-        <v>-7.922570307609929</v>
+        <v>-9.349081069936345</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.638341529976548</v>
       </c>
       <c r="E51">
-        <v>-14.10030253744278</v>
+        <v>-20.43425648960127</v>
       </c>
       <c r="F51">
-        <v>2.65345034005455</v>
+        <v>1.221869108006055</v>
       </c>
       <c r="G51">
-        <v>-7.292063667473575</v>
+        <v>-8.679109416426337</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.983945643385574</v>
       </c>
       <c r="E52">
-        <v>-12.39965676623221</v>
+        <v>-19.94262723743254</v>
       </c>
       <c r="F52">
-        <v>2.823129805374389</v>
+        <v>1.263087013234553</v>
       </c>
       <c r="G52">
-        <v>-7.91220830007201</v>
+        <v>-9.136587083407145</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.286967144825038</v>
       </c>
       <c r="E53">
-        <v>-12.54027041264439</v>
+        <v>-19.20569054826831</v>
       </c>
       <c r="F53">
-        <v>2.431323620993862</v>
+        <v>0.8695313168993137</v>
       </c>
       <c r="G53">
-        <v>-8.129419813994671</v>
+        <v>-9.322106744882362</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.541692065850555</v>
       </c>
       <c r="E54">
-        <v>-11.51458010685507</v>
+        <v>-19.96882445956692</v>
       </c>
       <c r="F54">
-        <v>2.652240923646462</v>
+        <v>1.431136251505683</v>
       </c>
       <c r="G54">
-        <v>-8.779852627731898</v>
+        <v>-9.309188996188126</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.750308190657883</v>
       </c>
       <c r="E55">
-        <v>-10.57586820133107</v>
+        <v>-18.05030927537333</v>
       </c>
       <c r="F55">
-        <v>2.567737508152079</v>
+        <v>1.194281160023221</v>
       </c>
       <c r="G55">
-        <v>-8.225673925548982</v>
+        <v>-9.973509548462596</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.908831495097157</v>
       </c>
       <c r="E56">
-        <v>-10.12898932930614</v>
+        <v>-18.93885021736634</v>
       </c>
       <c r="F56">
-        <v>2.527021593569678</v>
+        <v>1.151832300834163</v>
       </c>
       <c r="G56">
-        <v>-8.365153830209556</v>
+        <v>-9.522778773290826</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.00673828357028</v>
       </c>
       <c r="E57">
-        <v>-10.46015210501307</v>
+        <v>-17.52998308341799</v>
       </c>
       <c r="F57">
-        <v>2.345141933141408</v>
+        <v>0.9755176126178993</v>
       </c>
       <c r="G57">
-        <v>-8.149375782505398</v>
+        <v>-9.942059365839521</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.05003721700053</v>
       </c>
       <c r="E58">
-        <v>-9.220658955899609</v>
+        <v>-17.34500850562668</v>
       </c>
       <c r="F58">
-        <v>2.078672707008863</v>
+        <v>0.886854136026657</v>
       </c>
       <c r="G58">
-        <v>-9.052730964897405</v>
+        <v>-10.13618975626238</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.03704036535943</v>
       </c>
       <c r="E59">
-        <v>-8.322956910989074</v>
+        <v>-16.66158026533709</v>
       </c>
       <c r="F59">
-        <v>2.3768601209946</v>
+        <v>1.372269150393139</v>
       </c>
       <c r="G59">
-        <v>-7.685866301552039</v>
+        <v>-9.839624465763391</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.959024346097342</v>
       </c>
       <c r="E60">
-        <v>-8.754217076161545</v>
+        <v>-16.09495495512733</v>
       </c>
       <c r="F60">
-        <v>1.884541492693187</v>
+        <v>0.6433638216477703</v>
       </c>
       <c r="G60">
-        <v>-8.935120524069257</v>
+        <v>-10.22494879271578</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.821486361713145</v>
       </c>
       <c r="E61">
-        <v>-8.669996516566892</v>
+        <v>-15.50919684223517</v>
       </c>
       <c r="F61">
-        <v>1.623266130176195</v>
+        <v>0.8010667510579346</v>
       </c>
       <c r="G61">
-        <v>-8.612176806713354</v>
+        <v>-10.01215354654251</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.627023514082651</v>
       </c>
       <c r="E62">
-        <v>-7.733648474474901</v>
+        <v>-15.74586847929805</v>
       </c>
       <c r="F62">
-        <v>1.431832080124035</v>
+        <v>0.76840422436555</v>
       </c>
       <c r="G62">
-        <v>-7.708775276683796</v>
+        <v>-9.494212075832454</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.372362045610869</v>
       </c>
       <c r="E63">
-        <v>-7.643450329190122</v>
+        <v>-14.86354513211756</v>
       </c>
       <c r="F63">
-        <v>1.070251365536856</v>
+        <v>0.4201080378170671</v>
       </c>
       <c r="G63">
-        <v>-8.045477621300911</v>
+        <v>-9.42977561745608</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.059800269608948</v>
       </c>
       <c r="E64">
-        <v>-6.714184820446127</v>
+        <v>-15.91294199933704</v>
       </c>
       <c r="F64">
-        <v>1.241852643231191</v>
+        <v>0.7994779423793651</v>
       </c>
       <c r="G64">
-        <v>-7.655531772775698</v>
+        <v>-9.76854043194416</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.696805561446412</v>
       </c>
       <c r="E65">
-        <v>-5.586146473609448</v>
+        <v>-16.04004720778433</v>
       </c>
       <c r="F65">
-        <v>1.438894740600303</v>
+        <v>0.4986447229090855</v>
       </c>
       <c r="G65">
-        <v>-7.393031995875806</v>
+        <v>-9.276007398248012</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.28354341507451</v>
       </c>
       <c r="E66">
-        <v>-7.598129361321357</v>
+        <v>-15.0651844942571</v>
       </c>
       <c r="F66">
-        <v>1.176050450222409</v>
+        <v>0.2830844722503897</v>
       </c>
       <c r="G66">
-        <v>-7.393647757346111</v>
+        <v>-9.573916770235947</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.817613973536407</v>
       </c>
       <c r="E67">
-        <v>-7.042200306717721</v>
+        <v>-14.68563950225223</v>
       </c>
       <c r="F67">
-        <v>1.156984746079576</v>
+        <v>0.6610345550842893</v>
       </c>
       <c r="G67">
-        <v>-7.503839265620752</v>
+        <v>-10.16259135693807</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.307656913953712</v>
       </c>
       <c r="E68">
-        <v>-5.976437534434526</v>
+        <v>-15.27374789315437</v>
       </c>
       <c r="F68">
-        <v>0.8079803054016992</v>
+        <v>-0.2954232992101039</v>
       </c>
       <c r="G68">
-        <v>-6.628915048320006</v>
+        <v>-9.203645493850622</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.751506572080451</v>
       </c>
       <c r="E69">
-        <v>-5.866993374617149</v>
+        <v>-14.68611499202303</v>
       </c>
       <c r="F69">
-        <v>0.7278539832637086</v>
+        <v>0.4443999119041626</v>
       </c>
       <c r="G69">
-        <v>-7.762147891867926</v>
+        <v>-9.381537658403358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.142659180657515</v>
       </c>
       <c r="E70">
-        <v>-7.344888037864416</v>
+        <v>-15.2055173752808</v>
       </c>
       <c r="F70">
-        <v>0.6537291829590005</v>
+        <v>-0.2495607379541092</v>
       </c>
       <c r="G70">
-        <v>-6.632295115315602</v>
+        <v>-8.861361569454296</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.485008681739908</v>
       </c>
       <c r="E71">
-        <v>-5.898067763257782</v>
+        <v>-14.78572330629575</v>
       </c>
       <c r="F71">
-        <v>1.096745868547996</v>
+        <v>-0.1990957674081605</v>
       </c>
       <c r="G71">
-        <v>-6.474984612380513</v>
+        <v>-9.304527748068832</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.774436343550832</v>
       </c>
       <c r="E72">
-        <v>-5.601094966308768</v>
+        <v>-14.15652354224801</v>
       </c>
       <c r="F72">
-        <v>0.7472427506936339</v>
+        <v>-0.2271608550150078</v>
       </c>
       <c r="G72">
-        <v>-6.93900722789246</v>
+        <v>-9.238932598753713</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.004035238542467</v>
       </c>
       <c r="E73">
-        <v>-6.531623919300904</v>
+        <v>-14.70580932548239</v>
       </c>
       <c r="F73">
-        <v>0.5038891169362091</v>
+        <v>-0.329025194537263</v>
       </c>
       <c r="G73">
-        <v>-6.290156854923003</v>
+        <v>-8.709116201194291</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.177008807039638</v>
       </c>
       <c r="E74">
-        <v>-6.277540299678535</v>
+        <v>-15.75350801494899</v>
       </c>
       <c r="F74">
-        <v>0.7022002731664108</v>
+        <v>-0.158108148317641</v>
       </c>
       <c r="G74">
-        <v>-5.028166963716209</v>
+        <v>-8.530750628629439</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.294316057884927</v>
       </c>
       <c r="E75">
-        <v>-7.261224480572706</v>
+        <v>-14.84901325902695</v>
       </c>
       <c r="F75">
-        <v>0.2735541052811814</v>
+        <v>-0.4560652761654008</v>
       </c>
       <c r="G75">
-        <v>-5.466738105122237</v>
+        <v>-8.188671958056547</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.355514629019604</v>
       </c>
       <c r="E76">
-        <v>-6.762567036744077</v>
+        <v>-15.69078864994275</v>
       </c>
       <c r="F76">
-        <v>0.3619922659388622</v>
+        <v>-0.5798664412485924</v>
       </c>
       <c r="G76">
-        <v>-5.567325720787453</v>
+        <v>-8.131429315137009</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3674374487081917</v>
       </c>
       <c r="E77">
-        <v>-7.306382423377195</v>
+        <v>-14.94756643885588</v>
       </c>
       <c r="F77">
-        <v>0.3222703922398203</v>
+        <v>-0.4233165992631251</v>
       </c>
       <c r="G77">
-        <v>-5.280788072726915</v>
+        <v>-8.751577258280983</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.6567088501606685</v>
       </c>
       <c r="E78">
-        <v>-8.320353038434664</v>
+        <v>-16.61779897863093</v>
       </c>
       <c r="F78">
-        <v>0.1458770091202908</v>
+        <v>-0.2387919617177156</v>
       </c>
       <c r="G78">
-        <v>-4.5954985250067</v>
+        <v>-7.258067675330799</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.709014088600686</v>
       </c>
       <c r="E79">
-        <v>-8.314035817193965</v>
+        <v>-15.81668022735599</v>
       </c>
       <c r="F79">
-        <v>-0.004445995098332699</v>
+        <v>-0.6572748899379979</v>
       </c>
       <c r="G79">
-        <v>-3.638956117980762</v>
+        <v>-7.271488626947004</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.775731250208127</v>
       </c>
       <c r="E80">
-        <v>-9.263136042091556</v>
+        <v>-17.28898222520379</v>
       </c>
       <c r="F80">
-        <v>0.31334307673985</v>
+        <v>-0.481172263776851</v>
       </c>
       <c r="G80">
-        <v>-3.713949906081872</v>
+        <v>-7.633649066761115</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.833791886573256</v>
       </c>
       <c r="E81">
-        <v>-9.438578182096721</v>
+        <v>-17.59555991552307</v>
       </c>
       <c r="F81">
-        <v>0.6595418370244446</v>
+        <v>-0.1413014020822418</v>
       </c>
       <c r="G81">
-        <v>-3.330995929735599</v>
+        <v>-7.227746388736613</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.868519138700149</v>
       </c>
       <c r="E82">
-        <v>-10.97439202790209</v>
+        <v>-17.32462131564415</v>
       </c>
       <c r="F82">
-        <v>0.2460572777126546</v>
+        <v>-0.6652628368031935</v>
       </c>
       <c r="G82">
-        <v>-2.878606571248652</v>
+        <v>-6.960403283712769</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.862512496593391</v>
       </c>
       <c r="E83">
-        <v>-11.15799900654309</v>
+        <v>-19.78362798654923</v>
       </c>
       <c r="F83">
-        <v>0.4408544994201807</v>
+        <v>-0.1913405917831515</v>
       </c>
       <c r="G83">
-        <v>-2.492193074813841</v>
+        <v>-7.098539106884399</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>6.788060373055046</v>
       </c>
       <c r="E84">
-        <v>-12.66252109695546</v>
+        <v>-20.1100947347102</v>
       </c>
       <c r="F84">
-        <v>0.6963843056313554</v>
+        <v>-0.5222120700137469</v>
       </c>
       <c r="G84">
-        <v>-2.050245176957755</v>
+        <v>-6.919925243404101</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>7.628480964414939</v>
       </c>
       <c r="E85">
-        <v>-13.38422852803189</v>
+        <v>-20.93688540513462</v>
       </c>
       <c r="F85">
-        <v>0.3236123474323555</v>
+        <v>-0.3446100988535329</v>
       </c>
       <c r="G85">
-        <v>-2.556765265557325</v>
+        <v>-6.468241031117018</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>8.366453221127152</v>
       </c>
       <c r="E86">
-        <v>-15.67412386559453</v>
+        <v>-22.04717666233524</v>
       </c>
       <c r="F86">
-        <v>0.1758150354248677</v>
+        <v>-0.8020445190882535</v>
       </c>
       <c r="G86">
-        <v>-1.553123727144176</v>
+        <v>-6.541877495547027</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>8.981025651598298</v>
       </c>
       <c r="E87">
-        <v>-16.1616457918383</v>
+        <v>-21.87727737451547</v>
       </c>
       <c r="F87">
-        <v>0.5622608543418791</v>
+        <v>-0.7506161572528489</v>
       </c>
       <c r="G87">
-        <v>-1.81919558268094</v>
+        <v>-6.85092685327461</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>9.458200650907651</v>
       </c>
       <c r="E88">
-        <v>-17.21617794858247</v>
+        <v>-23.64481323529333</v>
       </c>
       <c r="F88">
-        <v>0.7732203524454264</v>
+        <v>-0.7693165513710478</v>
       </c>
       <c r="G88">
-        <v>-1.71694607315501</v>
+        <v>-6.990155156474199</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>9.790359019537748</v>
       </c>
       <c r="E89">
-        <v>-18.74374544321987</v>
+        <v>-26.14487505155195</v>
       </c>
       <c r="F89">
-        <v>0.2317828506276135</v>
+        <v>-0.6285901835138566</v>
       </c>
       <c r="G89">
-        <v>-1.795154400974753</v>
+        <v>-6.050271414601873</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>9.969331824855159</v>
       </c>
       <c r="E90">
-        <v>-21.06566162049075</v>
+        <v>-27.05924640928472</v>
       </c>
       <c r="F90">
-        <v>0.7068300185806572</v>
+        <v>-0.7446022099085245</v>
       </c>
       <c r="G90">
-        <v>-2.151451864638815</v>
+        <v>-6.689743012058575</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>9.992037275520024</v>
       </c>
       <c r="E91">
-        <v>-23.06241977858887</v>
+        <v>-27.79731068847686</v>
       </c>
       <c r="F91">
-        <v>0.78378203683112</v>
+        <v>-0.7393006585306077</v>
       </c>
       <c r="G91">
-        <v>-2.054479364702483</v>
+        <v>-6.378290198269481</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>9.865683088368918</v>
       </c>
       <c r="E92">
-        <v>-25.02511022672729</v>
+        <v>-29.57642132881832</v>
       </c>
       <c r="F92">
-        <v>0.5041641349139385</v>
+        <v>-1.003655891051208</v>
       </c>
       <c r="G92">
-        <v>-1.811001982471244</v>
+        <v>-6.779995104550186</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>9.597561174236441</v>
       </c>
       <c r="E93">
-        <v>-26.42974776595247</v>
+        <v>-31.95894207373385</v>
       </c>
       <c r="F93">
-        <v>0.860291706888488</v>
+        <v>-0.5449979721625529</v>
       </c>
       <c r="G93">
-        <v>-1.868125445751369</v>
+        <v>-6.898472908309623</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>9.195351180312992</v>
       </c>
       <c r="E94">
-        <v>-29.86650405256467</v>
+        <v>-33.69847385124828</v>
       </c>
       <c r="F94">
-        <v>1.050007722947242</v>
+        <v>-0.7041182381989072</v>
       </c>
       <c r="G94">
-        <v>-2.414017852449491</v>
+        <v>-5.671061665260516</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.683261660369237</v>
       </c>
       <c r="E95">
-        <v>-31.29630179337647</v>
+        <v>-34.76270373507988</v>
       </c>
       <c r="F95">
-        <v>1.205434298734513</v>
+        <v>-0.5164416626858456</v>
       </c>
       <c r="G95">
-        <v>-2.781604276402467</v>
+        <v>-6.872922117837528</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.072438564767705</v>
       </c>
       <c r="E96">
-        <v>-32.69725994747042</v>
+        <v>-37.19241117915534</v>
       </c>
       <c r="F96">
-        <v>1.216708379086614</v>
+        <v>-0.987829103453321</v>
       </c>
       <c r="G96">
-        <v>-2.322838807206884</v>
+        <v>-6.697065938791442</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>7.386636474673723</v>
       </c>
       <c r="E97">
-        <v>-35.40737276633783</v>
+        <v>-38.8983122444518</v>
       </c>
       <c r="F97">
-        <v>1.536880663942651</v>
+        <v>-0.4181707809569346</v>
       </c>
       <c r="G97">
-        <v>-2.732681034423118</v>
+        <v>-7.245245932457201</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.628881380036532</v>
       </c>
       <c r="E98">
-        <v>-38.27525988386947</v>
+        <v>-40.6463824597077</v>
       </c>
       <c r="F98">
-        <v>1.480992372010574</v>
+        <v>-0.315688479352191</v>
       </c>
       <c r="G98">
-        <v>-3.514045924238521</v>
+        <v>-7.049139146347394</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.848693135891321</v>
       </c>
       <c r="E99">
-        <v>-40.03932919779447</v>
+        <v>-43.0947789160128</v>
       </c>
       <c r="F99">
-        <v>1.747496389574037</v>
+        <v>-0.7527193820885569</v>
       </c>
       <c r="G99">
-        <v>-3.932412806218378</v>
+        <v>-8.016076666366644</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.005859191789794</v>
       </c>
       <c r="E100">
-        <v>-41.77805264269853</v>
+        <v>-45.21870794543133</v>
       </c>
       <c r="F100">
-        <v>1.860732556801924</v>
+        <v>-0.8695465220075795</v>
       </c>
       <c r="G100">
-        <v>-3.408128330255078</v>
+        <v>-7.80968732581186</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.190235125042258</v>
       </c>
       <c r="E101">
-        <v>-43.94493877655381</v>
+        <v>-47.09231878136486</v>
       </c>
       <c r="F101">
-        <v>1.874483455688396</v>
+        <v>-0.9836524750084059</v>
       </c>
       <c r="G101">
-        <v>-3.044766162410212</v>
+        <v>-7.755877718616547</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.281505816160581</v>
       </c>
       <c r="E102">
-        <v>-46.11585525227592</v>
+        <v>-48.47379770451482</v>
       </c>
       <c r="F102">
-        <v>1.727430017608622</v>
+        <v>-0.789465760076743</v>
       </c>
       <c r="G102">
-        <v>-4.912294559296178</v>
+        <v>-7.557933579732444</v>
       </c>
     </row>
   </sheetData>
